--- a/docs/oc-top-proveedores/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
+++ b/docs/oc-top-proveedores/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>29497.97</v>
+        <v>29308.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1420-6-CM26</t>
+          <t>747-23-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,27 +600,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>JULIÁN LEONARDO HIDALGO QUILODRÁN</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.992.223-4</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4328.97</v>
+        <v>5667.28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>747-23-CM26</t>
+          <t>1860-24-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,27 +661,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5791.89</v>
+        <v>5474.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1860-24-CM26</t>
+          <t>2279-127-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,42 +707,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5605.05</v>
+        <v>19407.85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2279-127-CM26</t>
+          <t>3654-75-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>61.101.034-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>20047.08</v>
+        <v>660.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3654-75-CM26</t>
+          <t>1057417-10664-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,27 +844,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.101.034-6</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>673.88</v>
+        <v>34533.22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057417-10664-CM26</t>
+          <t>1057417-10665-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>35483.34</v>
+        <v>26393.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1057417-10665-CM26</t>
+          <t>1057417-10698-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>27119.25</v>
+        <v>63924.39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057417-10698-CM26</t>
+          <t>2123-61-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>65683.16</v>
+        <v>46307.26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2328-318-CM26</t>
+          <t>2069-3343-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,27 +1088,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>JULIÁN LEONARDO HIDALGO QUILODRÁN</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10.992.223-4</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>37692.53</v>
+        <v>611308.61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2123-61-CM26</t>
+          <t>5441-182-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,27 +1149,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>45917.56</v>
+        <v>448.64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2069-3343-CM26</t>
+          <t>2279-170-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>603876.53</v>
+        <v>45694.56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5441-182-CM26</t>
+          <t>4468-46-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,37 +1261,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>443.19</v>
+        <v>35448.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2279-170-CM26</t>
+          <t>1121-36-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>45105.94</v>
+        <v>202.82</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4468-46-CM26</t>
+          <t>2279-210-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,27 +1393,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>34790.04</v>
+        <v>10630.64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1121-36-CM26</t>
+          <t>748-32-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,27 +1454,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>202.19</v>
+        <v>10406.21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2360-190-CM26</t>
+          <t>748-33-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,42 +1500,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3508.24</v>
+        <v>22350.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2279-210-CM26</t>
+          <t>2674-396-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10694.74</v>
+        <v>6511.14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>748-32-CM26</t>
+          <t>1176-39-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,37 +1627,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>10549.64</v>
+        <v>23758.03</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>748-33-CM26</t>
+          <t>511077-46-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>22658.99</v>
+        <v>4297.47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2674-396-CM26</t>
+          <t>1121-47-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,22 +1749,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6439.12</v>
+        <v>75.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1030177-70-CM26</t>
+          <t>568658-846-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,37 +1810,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>70.872.300-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>JULIÁN LEONARDO HIDALGO QUILODRÁN</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10.992.223-4</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>66743.77</v>
+        <v>26821.94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4454-395-CM26</t>
+          <t>1434-94-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.150.600-2</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI</t>
+          <t>Dirección General de Aeronáutica Civil</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>JULIÁN LEONARDO HIDALGO QUILODRÁN</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>10.992.223-4</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>13179.03</v>
+        <v>403185.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>511077-46-CM26</t>
+          <t>1488-545-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,27 +1942,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4344.74</v>
+        <v>64684.58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1121-47-CM26</t>
+          <t>1488-546-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>75.42</v>
+        <v>27721.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>568658-846-CM26</t>
+          <t>1488-639-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,27 +2064,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>26736.84</v>
+        <v>25279.97</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1434-94-CM26</t>
+          <t>2771-286-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,27 +2125,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>69.264.700-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>401052.58</v>
+        <v>104061.33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1488-545-CM26</t>
+          <t>3477-444-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,22 +2176,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>65088.11</v>
+        <v>27231.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1488-546-CM26</t>
+          <t>1078629-11-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>SEREMI LA ARAUCANIA FONDOS EXTRAPRESUPUESTARIOS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>27894.91</v>
+        <v>22206.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1488-639-CM26</t>
+          <t>1525570-26-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,37 +2298,37 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>65.229.008-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNIT</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>25437.68</v>
+        <v>1909.96</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2771-286-CM26</t>
+          <t>748-51-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,27 +2369,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.264.700-9</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>103347.8</v>
+        <v>1375.98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3477-444-CM26</t>
+          <t>2546-635-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>27147.91</v>
+        <v>11709.35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1078629-11-CM26</t>
+          <t>1062807-63-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,37 +2481,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SEREMI LA ARAUCANIA FONDOS EXTRAPRESUPUESTARIOS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>22138.31</v>
+        <v>216839.78</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1525570-26-CM26</t>
+          <t>1057417-13722-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,27 +2552,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.229.008-6</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNIT</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1915.02</v>
+        <v>40430.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>748-51-CM26</t>
+          <t>837-410-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,27 +2613,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1379.63</v>
+        <v>2803.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2360-405-CM26</t>
+          <t>1060500-16-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,27 +2674,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>62.000.510-k</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES REGION DE NUBLE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>17934.88</v>
+        <v>20863.75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2416-170-CM26</t>
+          <t>5485-464-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,27 +2735,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2213.9</v>
+        <v>409.01</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2416-171-CM26</t>
+          <t>652-186-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1372.62</v>
+        <v>12890.69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2546-635-CM26</t>
+          <t>5485-472-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,42 +2842,42 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>11955.05</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1062807-63-CM26</t>
+          <t>752-187-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,27 +2918,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>221389.72</v>
+        <v>19108.48</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1057417-13722-CM26</t>
+          <t>1178-37-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,27 +2979,27 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>40049.63</v>
+        <v>46114.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>837-410-CM26</t>
+          <t>5485-481-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.003.000-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2792.79</v>
+        <v>216.23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1060500-16-CM26</t>
+          <t>5751-168-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,27 +3101,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>62.000.510-k</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES REGION DE NUBLE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>20782.62</v>
+        <v>194424.62</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5485-464-CM26</t>
+          <t>1488-1054-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,37 +3152,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>404.95</v>
+        <v>9732.040000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4886-60-CM26</t>
+          <t>2291-1223-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,37 +3213,37 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>857.17</v>
+        <v>4866.02</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5485-472-CM26</t>
+          <t>1523-1545-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,37 +3274,37 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>97.75</v>
+        <v>12330.98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>652-186-CM26</t>
+          <t>2792-412-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,27 +3345,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>Iluste Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>12825.33</v>
+        <v>32122.67</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>752-187-CM26</t>
+          <t>1488-1053-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,37 +3396,37 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>19205.77</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5485-481-CM26</t>
+          <t>1485217-105-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,22 +3457,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>214.83</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5751-168-CM26</t>
+          <t>1121-73-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,27 +3528,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>193131.89</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1488-1054-CM26</t>
+          <t>4732-179-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,37 +3579,37 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>9667.34</v>
+        <v>47837.79</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2291-1223-CM26</t>
+          <t>2407-490-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,27 +3650,27 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>4833.67</v>
+        <v>7638.09</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1523-1545-CM26</t>
+          <t>2467-894-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,27 +3711,27 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>12245.28</v>
+        <v>1817.07</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2792-412-CM26</t>
+          <t>1057417-14563-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,27 +3772,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>32224.45</v>
+        <v>43703.37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1488-1053-CM26</t>
+          <t>1549-3384-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,37 +3823,37 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>64448.86</v>
+        <v>11354.05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2416-187-CM26</t>
+          <t>1306643-258-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,27 +3894,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>46725.46</v>
+        <v>156443.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1485217-105-CM26</t>
+          <t>1178-45-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,27 +3955,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Coquimbo </t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7218.28</v>
+        <v>183957.01</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1121-73-CM26</t>
+          <t>1488-904-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,42 +4001,42 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de la Araucanía </t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>144.53</v>
+        <v>83035.34</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4732-179-CM26</t>
+          <t>1488-903-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,42 +4062,42 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t xml:space="preserve">Región de la Araucanía </t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>47933.88</v>
+        <v>208859.42</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2416-186-CM26</t>
+          <t>1134432-566-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,27 +4138,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>44061.57</v>
+        <v>9720.629999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2407-490-CM26</t>
+          <t>564953-778-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,27 +4199,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>7680.67</v>
+        <v>5594.68</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2467-894-CM26</t>
+          <t>675-43-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,22 +4260,22 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.402.019-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t xml:space="preserve">Región del Maule </t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1826.05</v>
+        <v>10942.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4886-97-CM26</t>
+          <t>1860-62-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,27 +4321,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t xml:space="preserve">Región de los Lagos </t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>212.68</v>
+        <v>8202.01</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1057417-14563-CM26</t>
+          <t>2852-777-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,27 +4382,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>43412.78</v>
+        <v>6558.98</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1549-3384-CM26</t>
+          <t>2792-553-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,27 +4443,27 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,7 +4473,800 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>11278.56</v>
+        <v>29566.36</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1443565-35-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.312.000-9</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>INIA</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>20457.74</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1523-1816-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>61.602.236-9</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>16.995.419-4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>249028.09</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1208093-61-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>4375.46</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1385462-131-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>11707.46</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1495207-11-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>11707.46</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1495208-17-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>11707.46</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1078634-13-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.402.010-5</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>David Isaac</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>43733.05</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>967490-77-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>60.505.000-K</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>76.310.505-9</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>11737.55</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1057499-443-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.608.108-K</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>20687.7</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1057499-444-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>61.608.108-K</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>9472.790000000001</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1057499-445-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>61.608.108-K</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>9554.450000000001</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1443565-45-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>61.312.000-9</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>INIA</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Región de Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>408.91</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2793-854-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>69.255.400-0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Municipalidad de Huechuraba</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>36806.65</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-proveedores/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
+++ b/docs/oc-top-proveedores/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="transporte-priva top prov" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="transporte-priva top prov" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">

--- a/docs/oc-top-proveedores/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
+++ b/docs/oc-top-proveedores/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1860-24-CM26</t>
+          <t>2279-127-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,42 +646,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5474.63</v>
+        <v>19407.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2279-127-CM26</t>
+          <t>1057417-10664-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,37 +712,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>19407.85</v>
+        <v>34533.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3654-75-CM26</t>
+          <t>1057417-10665-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,27 +783,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.101.034-6</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>660.59</v>
+        <v>26393.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057417-10664-CM26</t>
+          <t>1057417-10698-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>34533.22</v>
+        <v>63924.39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057417-10665-CM26</t>
+          <t>2123-61-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,27 +905,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>26393.09</v>
+        <v>46307.26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1057417-10698-CM26</t>
+          <t>2069-3343-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,37 +956,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>63924.39</v>
+        <v>611308.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2123-61-CM26</t>
+          <t>2279-170-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,27 +1017,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.071.100-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>46307.26</v>
+        <v>45694.56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2069-3343-CM26</t>
+          <t>4468-46-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,17 +1088,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>611308.61</v>
+        <v>35448.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5441-182-CM26</t>
+          <t>1161266-265-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,37 +1139,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.141.800-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>448.64</v>
+        <v>25721.89</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2279-170-CM26</t>
+          <t>2279-210-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>45694.56</v>
+        <v>10630.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4468-46-CM26</t>
+          <t>748-32-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>35448.02</v>
+        <v>10406.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1121-36-CM26</t>
+          <t>748-33-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>202.82</v>
+        <v>22350.92</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2279-210-CM26</t>
+          <t>2674-396-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.071.100-1</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10630.64</v>
+        <v>6511.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>748-32-CM26</t>
+          <t>1176-39-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,37 +1444,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10406.21</v>
+        <v>23758.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>748-33-CM26</t>
+          <t>511077-46-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1525,17 +1525,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>22350.92</v>
+        <v>4297.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2674-396-CM26</t>
+          <t>1434-94-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6511.14</v>
+        <v>403185.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1176-39-CM26</t>
+          <t>1488-545-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,42 +1622,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>23758.03</v>
+        <v>64684.58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>511077-46-CM26</t>
+          <t>1488-546-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,27 +1698,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4297.47</v>
+        <v>27721.96</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1121-47-CM26</t>
+          <t>1488-639-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>75.23</v>
+        <v>25279.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>568658-846-CM26</t>
+          <t>3477-444-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,42 +1805,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.872.300-2</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL VINA DEL MAR PARA EL DESARROLLO SOCIAL</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>26821.94</v>
+        <v>27231.85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1434-94-CM26</t>
+          <t>1078629-11-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,42 +1866,42 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>403185.16</v>
+        <v>22206.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1488-545-CM26</t>
+          <t>1525570-26-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,37 +1932,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>65.229.008-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>64684.58</v>
+        <v>1909.96</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1488-546-CM26</t>
+          <t>748-51-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>27721.96</v>
+        <v>1375.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1488-639-CM26</t>
+          <t>2546-635-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>25279.97</v>
+        <v>11709.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2771-286-CM26</t>
+          <t>1062807-63-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,27 +2125,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.264.700-9</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>104061.33</v>
+        <v>216839.78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3477-444-CM26</t>
+          <t>1057417-13722-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,42 +2171,42 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>27231.85</v>
+        <v>40430.05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1078629-11-CM26</t>
+          <t>837-410-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,27 +2247,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SEREMI LA ARAUCANIA FONDOS EXTRAPRESUPUESTARIOS</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>22206.75</v>
+        <v>2803.69</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1525570-26-CM26</t>
+          <t>1060500-16-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,42 +2293,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>65.229.008-6</t>
+          <t>62.000.510-k</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNIT</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1909.96</v>
+        <v>20863.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>748-51-CM26</t>
+          <t>5485-464-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,27 +2369,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1375.98</v>
+        <v>409.01</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2546-635-CM26</t>
+          <t>652-186-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,27 +2430,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>11709.35</v>
+        <v>12890.69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1062807-63-CM26</t>
+          <t>5485-472-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,42 +2476,42 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>216839.78</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1057417-13722-CM26</t>
+          <t>2409-646-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>40430.05</v>
+        <v>12400.79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>837-410-CM26</t>
+          <t>2409-608-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,27 +2613,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.003.000-9</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2803.69</v>
+        <v>5391.65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1060500-16-CM26</t>
+          <t>752-187-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,27 +2674,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>62.000.510-k</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES REGION DE NUBLE</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>20863.75</v>
+        <v>19108.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5485-464-CM26</t>
+          <t>1178-37-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,27 +2735,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>409.01</v>
+        <v>46114.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>652-186-CM26</t>
+          <t>5485-481-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,27 +2786,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>12890.69</v>
+        <v>216.23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5485-472-CM26</t>
+          <t>5751-168-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,27 +2847,27 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>98.25</v>
+        <v>194424.62</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>752-187-CM26</t>
+          <t>1488-1054-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,37 +2908,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>19108.48</v>
+        <v>9732.040000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1178-37-CM26</t>
+          <t>2291-1223-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,27 +2979,27 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>46114.6</v>
+        <v>4866.02</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5485-481-CM26</t>
+          <t>1523-1545-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,37 +3030,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>216.23</v>
+        <v>12330.98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5751-168-CM26</t>
+          <t>2792-412-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,27 +3101,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>194424.62</v>
+        <v>32122.67</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1488-1054-CM26</t>
+          <t>1488-1053-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>9732.040000000001</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2291-1223-CM26</t>
+          <t>1485217-105-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,37 +3213,37 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4866.02</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1523-1545-CM26</t>
+          <t>4732-179-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>12330.98</v>
+        <v>47837.79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2792-412-CM26</t>
+          <t>2407-490-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>32122.67</v>
+        <v>7638.09</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1488-1053-CM26</t>
+          <t>4358-141-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,37 +3396,37 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>64308.63</v>
+        <v>9133.049999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1485217-105-CM26</t>
+          <t>2467-894-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,27 +3467,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>7203.81</v>
+        <v>1817.07</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1121-73-CM26</t>
+          <t>1057417-14563-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,27 +3528,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>144.24</v>
+        <v>43703.37</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4732-179-CM26</t>
+          <t>1549-3384-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,27 +3589,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>47837.79</v>
+        <v>11354.05</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2407-490-CM26</t>
+          <t>1306643-258-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>7638.09</v>
+        <v>156443.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2467-894-CM26</t>
+          <t>1488-903-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,42 +3696,42 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1817.07</v>
+        <v>208859.42</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057417-14563-CM26</t>
+          <t>1488-904-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,42 +3757,42 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>43703.37</v>
+        <v>83035.34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1549-3384-CM26</t>
+          <t>1178-45-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,27 +3833,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>11354.05</v>
+        <v>183957.01</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1306643-258-CM26</t>
+          <t>564953-778-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>156443.2</v>
+        <v>5594.68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1178-45-CM26</t>
+          <t>2408-724-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,27 +3955,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>183957.01</v>
+        <v>14179.41</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1488-904-CM26</t>
+          <t>675-43-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,37 +4006,37 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.402.019-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>83035.34</v>
+        <v>10942.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1488-903-CM26</t>
+          <t>2852-777-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,27 +4077,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>208859.42</v>
+        <v>6558.98</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1134432-566-CM26</t>
+          <t>4081-278-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,27 +4138,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>9720.629999999999</v>
+        <v>4385.96</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>564953-778-CM26</t>
+          <t>2792-553-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Corporación de Educación y Salud de Las Condes</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>5594.68</v>
+        <v>29566.36</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>675-43-CM26</t>
+          <t>1523-1816-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,27 +4260,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.402.019-9</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>16.995.419-4</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>10942.6</v>
+        <v>249028.09</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1860-62-CM26</t>
+          <t>4358-167-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,27 +4321,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>8202.01</v>
+        <v>3821.94</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2852-777-CM26</t>
+          <t>1385462-131-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,27 +4382,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>6558.98</v>
+        <v>11707.46</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2792-553-CM26</t>
+          <t>1495207-11-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,27 +4443,27 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>29566.36</v>
+        <v>11707.46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1443565-35-CM26</t>
+          <t>1495208-17-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,27 +4504,27 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>20457.74</v>
+        <v>11707.46</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1523-1816-CM26</t>
+          <t>2408-777-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,27 +4565,27 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>16.995.419-4</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>249028.09</v>
+        <v>10663.29</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1208093-61-CM26</t>
+          <t>1078634-13-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,27 +4626,27 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.402.010-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>4375.46</v>
+        <v>43733.05</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1385462-131-CM26</t>
+          <t>1057417-15339-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,27 +4687,27 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>11707.46</v>
+        <v>42076.74</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1495207-11-CM26</t>
+          <t>1057499-445-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,17 +4748,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>11707.46</v>
+        <v>9554.450000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1495208-17-CM26</t>
+          <t>1057499-443-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,17 +4809,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>11707.46</v>
+        <v>20687.7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1078634-13-CM26</t>
+          <t>967490-77-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,37 +4860,37 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.402.010-5</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>43733.05</v>
+        <v>11737.55</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>967490-77-CM26</t>
+          <t>1057499-444-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>11737.55</v>
+        <v>9472.790000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1057499-443-CM26</t>
+          <t>2793-854-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>20687.7</v>
+        <v>36806.65</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1057499-444-CM26</t>
+          <t>1079576-942-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,17 +5053,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>9472.790000000001</v>
+        <v>6342.49</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1057499-445-CM26</t>
+          <t>1385462-164-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>9554.450000000001</v>
+        <v>13606.17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1443565-45-CM26</t>
+          <t>1495199-11-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,27 +5175,27 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>408.91</v>
+        <v>13606.17</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2793-854-CM26</t>
+          <t>1057532-1385-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,17 +5236,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5266,7 +5266,1044 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>36806.65</v>
+        <v>7476.08</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3316-189-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>61.979.960-7</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>76.310.505-9</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>15283.35</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1488-1234-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>61.602.232-6</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>TRANSERVI JL SPA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>46989.46</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1079659-376-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>61.980.860-6</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.310.505-9</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>14866.12</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>4081-301-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>69.151.001-8</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>14935.69</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>933-88-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>3841.35</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>933-70-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>85024.07000000001</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2409-1207-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>69.170.101-8</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>10456.68</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>748-79-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>TRANSERVI JL SPA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>7309.89</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>748-81-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>TRANSERVI JL SPA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>2327.35</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2713-1059-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>76.238.635-6</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>11010</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>678-45-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>61.402.018-0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>76.701.245-4</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>21007.77</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>678-46-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>61.402.018-0</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>76.701.245-4</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>15729.88</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>933-95-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>317.17</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>654-323-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>61.820.004-3</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>David Isaac</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>27910.81</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1077367-61-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>61.607.301-k</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>41230.37</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1057417-16197-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>22013.99</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1469-2823-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>933.51</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-proveedores/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
+++ b/docs/oc-top-proveedores/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1062,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1249,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1436,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1562,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1795,7 +1823,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3477-444-CM26</t>
+          <t>1078629-11-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,17 +1843,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1863,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1878,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>27231.85</v>
+        <v>22206.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1078629-11-CM26</t>
+          <t>3477-444-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,17 +1904,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,28 +1924,32 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>22206.75</v>
+        <v>27231.85</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1525570-26-CM26</t>
+          <t>748-51-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,32 +1969,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>65.229.008-6</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +2004,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1909.96</v>
+        <v>1375.98</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>748-51-CM26</t>
+          <t>1525570-26-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,42 +2030,46 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>65.229.008-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1375.98</v>
+        <v>1909.96</v>
       </c>
     </row>
     <row r="27">
@@ -2270,7 +2306,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2432,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2405,7 +2449,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>652-186-CM26</t>
+          <t>5485-472-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2425,22 +2469,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2453,20 +2497,24 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>12890.69</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5485-472-CM26</t>
+          <t>652-186-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,22 +2534,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2514,20 +2562,24 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>98.25</v>
+        <v>12890.69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2409-646-CM26</t>
+          <t>2409-608-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2582,13 +2634,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>12400.79</v>
+        <v>5391.65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2409-608-CM26</t>
+          <t>2409-646-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2643,7 +2695,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5391.65</v>
+        <v>12400.79</v>
       </c>
     </row>
     <row r="37">
@@ -2697,7 +2749,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2875,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2940,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3066,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3192,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3137,7 +3209,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1488-1053-CM26</t>
+          <t>3894-54-SE26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,53 +3224,57 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>64308.63</v>
+        <v>12849.07</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1485217-105-CM26</t>
+          <t>1488-1053-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3289,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,27 +3299,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3329,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7203.81</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4732-179-CM26</t>
+          <t>1485217-105-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3279,32 +3355,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3390,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>47837.79</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2407-490-CM26</t>
+          <t>4732-179-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3411,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,27 +3421,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3451,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>7638.09</v>
+        <v>47837.79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4358-141-CM26</t>
+          <t>2407-490-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3406,43 +3482,47 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>9133.049999999999</v>
+        <v>7638.09</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2467-894-CM26</t>
+          <t>4358-141-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3537,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,27 +3547,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3577,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1817.07</v>
+        <v>9133.049999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1057417-14563-CM26</t>
+          <t>2467-894-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3598,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,27 +3608,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3638,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>43703.37</v>
+        <v>1817.07</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1549-3384-CM26</t>
+          <t>1057417-14563-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,27 +3669,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3699,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>11354.05</v>
+        <v>43703.37</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1306643-258-CM26</t>
+          <t>1549-3384-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3635,12 +3715,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3730,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3673,20 +3753,24 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>156443.2</v>
+        <v>11354.05</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1488-903-CM26</t>
+          <t>1306643-258-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,53 +3785,57 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>208859.42</v>
+        <v>156443.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1488-904-CM26</t>
+          <t>1488-903-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3802,13 +3890,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>83035.34</v>
+        <v>208859.42</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1178-45-CM26</t>
+          <t>1488-904-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3828,32 +3916,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3951,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>183957.01</v>
+        <v>83035.34</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>564953-778-CM26</t>
+          <t>1178-45-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3972,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,27 +3982,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Corporación de Educación y Salud de Las Condes</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +4012,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5594.68</v>
+        <v>183957.01</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2408-724-CM26</t>
+          <t>564953-778-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +4033,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,43 +4043,47 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>14179.41</v>
+        <v>5594.68</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>675-43-CM26</t>
+          <t>2408-724-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4016,27 +4108,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.402.019-9</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4138,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>10942.6</v>
+        <v>14179.41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2852-777-CM26</t>
+          <t>675-43-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,37 +4159,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.402.019-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4199,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>6558.98</v>
+        <v>10942.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4081-278-CM26</t>
+          <t>2852-777-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,37 +4220,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4260,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4385.96</v>
+        <v>6558.98</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2792-553-CM26</t>
+          <t>4081-278-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4281,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,27 +4291,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4321,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>29566.36</v>
+        <v>4385.96</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1523-1816-CM26</t>
+          <t>2792-553-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4342,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,43 +4352,47 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>16.995.419-4</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>249028.09</v>
+        <v>29566.36</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4358-167-CM26</t>
+          <t>1523-1816-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4321,27 +4417,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>16.995.419-4</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4447,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>3821.94</v>
+        <v>249028.09</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1385462-131-CM26</t>
+          <t>4358-167-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4468,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,27 +4478,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4508,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>11707.46</v>
+        <v>3821.94</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1495207-11-CM26</t>
+          <t>1385462-131-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4453,20 +4549,24 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4479,7 +4579,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1495208-17-CM26</t>
+          <t>1495207-11-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4514,7 +4614,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4527,7 +4627,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4540,7 +4644,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2408-777-CM26</t>
+          <t>1495208-17-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4659,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,43 +4669,47 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>10663.29</v>
+        <v>11707.46</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1078634-13-CM26</t>
+          <t>2408-777-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4724,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,27 +4734,27 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.402.010-5</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4764,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>43733.05</v>
+        <v>10663.29</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1057417-15339-CM26</t>
+          <t>1078634-13-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4785,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,27 +4795,27 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.402.010-5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4825,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>42076.74</v>
+        <v>43733.05</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1057499-445-CM26</t>
+          <t>1057417-15339-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4846,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,27 +4856,27 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4886,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>9554.450000000001</v>
+        <v>42076.74</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1057499-443-CM26</t>
+          <t>1057499-445-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4832,20 +4940,24 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>20687.7</v>
+        <v>9554.450000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>967490-77-CM26</t>
+          <t>1057499-444-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4865,17 +4977,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,28 +4997,32 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>11737.55</v>
+        <v>9472.790000000001</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057499-444-CM26</t>
+          <t>967490-77-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4926,17 +5042,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +5062,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +5077,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>9472.790000000001</v>
+        <v>11737.55</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2793-854-CM26</t>
+          <t>1057499-443-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +5098,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +5108,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5015,20 +5131,24 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>36806.65</v>
+        <v>20687.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1079576-942-CM26</t>
+          <t>2793-854-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5038,12 +5158,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,17 +5173,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5076,20 +5196,24 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>6342.49</v>
+        <v>36806.65</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1385462-164-CM26</t>
+          <t>1079576-942-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5114,17 +5238,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5137,20 +5261,24 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>13606.17</v>
+        <v>6342.49</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1495199-11-CM26</t>
+          <t>1385462-164-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5185,7 +5313,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5198,7 +5326,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5211,7 +5343,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1057532-1385-CM26</t>
+          <t>1495199-11-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5358,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,17 +5368,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5259,20 +5391,24 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>7476.08</v>
+        <v>13606.17</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3316-189-CM26</t>
+          <t>1057532-1385-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,53 +5423,57 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>15283.35</v>
+        <v>7476.08</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1488-1234-CM26</t>
+          <t>3316-189-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,37 +5488,37 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5528,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>46989.46</v>
+        <v>15283.35</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1079659-376-CM26</t>
+          <t>1488-1234-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,22 +5549,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5574,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5589,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>14866.12</v>
+        <v>46989.46</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4081-301-CM26</t>
+          <t>1079659-376-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,37 +5610,37 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5650,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>14935.69</v>
+        <v>14866.12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>933-88-CM26</t>
+          <t>4081-301-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5671,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,12 +5681,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5571,13 +5711,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3841.35</v>
+        <v>14935.69</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>933-70-CM26</t>
+          <t>933-88-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,12 +5732,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5632,13 +5772,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>85024.07000000001</v>
+        <v>3841.35</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2409-1207-CM26</t>
+          <t>933-70-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,22 +5793,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,13 +5833,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>10456.68</v>
+        <v>85024.07000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>748-79-CM26</t>
+          <t>2409-1207-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5719,32 +5859,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5894,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>7309.89</v>
+        <v>10456.68</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>748-81-CM26</t>
+          <t>748-79-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5780,7 +5920,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5815,13 +5955,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2327.35</v>
+        <v>7309.89</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2713-1059-CM26</t>
+          <t>748-81-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,7 +5976,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,27 +5986,27 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +6016,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>11010</v>
+        <v>2327.35</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>678-45-CM26</t>
+          <t>2713-1059-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5907,27 +6047,27 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +6077,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>21007.77</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>678-46-CM26</t>
+          <t>678-45-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5998,13 +6138,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>15729.88</v>
+        <v>21007.77</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>933-95-CM26</t>
+          <t>678-46-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6159,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,27 +6169,27 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6199,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>317.17</v>
+        <v>15729.88</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>654-323-CM26</t>
+          <t>933-95-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6090,12 +6230,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,28 +6245,32 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>27910.81</v>
+        <v>317.17</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1077367-61-CM26</t>
+          <t>654-323-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,7 +6285,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6295,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.607.301-k</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6310,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6325,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>41230.37</v>
+        <v>27910.81</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1057417-16197-CM26</t>
+          <t>1077367-61-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6212,7 +6356,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.607.301-k</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6242,13 +6386,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>22013.99</v>
+        <v>41230.37</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1469-2823-CM26</t>
+          <t>1057417-16197-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6407,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,27 +6417,27 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,6 +6447,71 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
+        <v>22013.99</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1469-2823-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
         <v>933.51</v>
       </c>
     </row>

--- a/docs/oc-top-proveedores/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
+++ b/docs/oc-top-proveedores/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -627,7 +627,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -705,7 +709,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057417-10664-CM26</t>
+          <t>1057417-10698-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -753,20 +757,24 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>34533.22</v>
+        <v>63924.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1057417-10665-CM26</t>
+          <t>1057417-10664-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -814,20 +822,24 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>26393.09</v>
+        <v>34533.22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057417-10698-CM26</t>
+          <t>1057417-10665-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -875,14 +887,18 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>63924.39</v>
+        <v>26393.09</v>
       </c>
     </row>
     <row r="8">
@@ -1564,7 +1580,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1640,7 +1656,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1488-545-CM26</t>
+          <t>1488-639-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,7 +1711,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>64684.58</v>
+        <v>25279.97</v>
       </c>
     </row>
     <row r="21">
@@ -1762,7 +1778,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1488-639-CM26</t>
+          <t>1488-545-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1817,13 +1833,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>25279.97</v>
+        <v>64684.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1078629-11-CM26</t>
+          <t>3477-444-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1843,17 +1859,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1863,28 +1879,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>22206.75</v>
+        <v>27231.85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3477-444-CM26</t>
+          <t>1078629-11-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1904,17 +1924,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1924,17 +1944,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1943,7 +1963,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>27231.85</v>
+        <v>22206.75</v>
       </c>
     </row>
     <row r="25">
@@ -2060,7 +2080,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2245,7 +2265,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2258,7 +2282,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>837-410-CM26</t>
+          <t>1060500-16-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2283,47 +2307,43 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.003.000-9</t>
+          <t>62.000.510-k</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2803.69</v>
+        <v>20863.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1060500-16-CM26</t>
+          <t>837-410-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2348,37 +2368,41 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>62.000.510-k</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>20863.75</v>
+        <v>2803.69</v>
       </c>
     </row>
     <row r="32">
@@ -2434,7 +2458,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2449,7 +2473,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5485-472-CM26</t>
+          <t>652-186-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2469,22 +2493,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2499,7 +2523,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2508,13 +2532,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>98.25</v>
+        <v>12890.69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>652-186-CM26</t>
+          <t>5485-472-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2534,22 +2558,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2564,7 +2588,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2573,13 +2597,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12890.69</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2409-608-CM26</t>
+          <t>2409-646-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2634,13 +2658,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5391.65</v>
+        <v>12400.79</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2409-646-CM26</t>
+          <t>2409-608-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2695,7 +2719,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>12400.79</v>
+        <v>5391.65</v>
       </c>
     </row>
     <row r="37">
@@ -2751,7 +2775,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2877,7 +2901,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2942,7 +2966,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2957,7 +2981,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1488-1054-CM26</t>
+          <t>2291-1223-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2977,48 +3001,52 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>9732.040000000001</v>
+        <v>4866.02</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2291-1223-CM26</t>
+          <t>1488-1054-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3038,46 +3066,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>4866.02</v>
+        <v>9732.040000000001</v>
       </c>
     </row>
     <row r="43">
@@ -3335,7 +3359,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1485217-105-CM26</t>
+          <t>4732-179-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3355,32 +3379,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3390,13 +3414,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>7203.81</v>
+        <v>47837.79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4732-179-CM26</t>
+          <t>1485217-105-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3416,32 +3440,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3451,7 +3475,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>47837.79</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="49">
@@ -3692,7 +3716,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3755,7 +3783,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3820,7 +3848,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3835,7 +3863,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1488-903-CM26</t>
+          <t>1488-904-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3890,13 +3918,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>208859.42</v>
+        <v>83035.34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1488-904-CM26</t>
+          <t>1178-45-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3916,32 +3944,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3951,13 +3979,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>83035.34</v>
+        <v>183957.01</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1178-45-CM26</t>
+          <t>1488-903-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3977,32 +4005,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -4012,7 +4040,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>183957.01</v>
+        <v>208859.42</v>
       </c>
     </row>
     <row r="58">
@@ -4068,7 +4096,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4514,7 +4542,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1385462-131-CM26</t>
+          <t>1495207-11-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4549,7 +4577,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4564,7 +4592,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4579,7 +4607,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1495207-11-CM26</t>
+          <t>1385462-131-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4614,7 +4642,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4629,7 +4657,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4694,7 +4722,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4942,7 +4970,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5007,7 +5035,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,7 +5050,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>967490-77-CM26</t>
+          <t>1057499-443-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5042,17 +5070,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5062,28 +5090,32 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>11737.55</v>
+        <v>20687.7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1057499-443-CM26</t>
+          <t>967490-77-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5103,17 +5135,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5123,26 +5155,22 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.310.505-9</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>20687.7</v>
+        <v>11737.55</v>
       </c>
     </row>
     <row r="76">
@@ -5198,7 +5226,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5213,7 +5241,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1079576-942-CM26</t>
+          <t>1385462-164-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5238,17 +5266,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5263,7 +5291,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5272,13 +5300,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>6342.49</v>
+        <v>13606.17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1385462-164-CM26</t>
+          <t>1495199-11-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5313,7 +5341,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5328,7 +5356,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5343,7 +5371,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1495199-11-CM26</t>
+          <t>1079576-942-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5363,22 +5391,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5393,7 +5421,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5402,7 +5430,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>13606.17</v>
+        <v>6342.49</v>
       </c>
     </row>
     <row r="80">
@@ -5458,7 +5486,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5554,7 +5582,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5839,7 +5867,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2409-1207-CM26</t>
+          <t>748-79-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5859,32 +5887,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5894,13 +5922,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>10456.68</v>
+        <v>7309.89</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>748-79-CM26</t>
+          <t>2409-1207-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5920,32 +5948,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5955,7 +5983,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>7309.89</v>
+        <v>10456.68</v>
       </c>
     </row>
     <row r="89">
@@ -5981,7 +6009,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6022,7 +6050,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2713-1059-CM26</t>
+          <t>678-46-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6042,42 +6070,46 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>76.701.245-4</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>11010</v>
+        <v>15729.88</v>
       </c>
     </row>
     <row r="91">
@@ -6103,7 +6135,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6131,7 +6163,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6144,7 +6180,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>678-46-CM26</t>
+          <t>2713-1059-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6169,27 +6205,27 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6199,13 +6235,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>15729.88</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>933-95-CM26</t>
+          <t>654-323-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6230,12 +6266,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6245,32 +6281,28 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>317.17</v>
+        <v>27910.81</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>654-323-CM26</t>
+          <t>933-95-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6295,12 +6327,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6310,22 +6342,26 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>27910.81</v>
+        <v>317.17</v>
       </c>
     </row>
     <row r="95">
@@ -6503,7 +6539,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6513,6 +6549,518 @@
       </c>
       <c r="M97" s="2" t="n">
         <v>933.51</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1705-646-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>61.606.603-k</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>FEBGIP SPA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>5836.21</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2069-8569-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>76.238.635-6</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>590228.25</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1495206-7-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>10232.8</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>5485-733-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>71.31</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1457776-43-SE26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>60.501.000-8</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>51670.16</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1777-96-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>60.804.012-9</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>David Isaac</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>211983.43</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2292-7344-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>11670.52</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1057417-17061-SE26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>76.701.245-4</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>314520.87</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-proveedores/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
+++ b/docs/oc-top-proveedores/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
@@ -989,7 +989,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
